--- a/Team-Data/2011-12/4-23-2011-12.xlsx
+++ b/Team-Data/2011-12/4-23-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
@@ -933,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -951,7 +1018,7 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.109</v>
+        <v>0.111</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="J4" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="L4" t="n">
         <v>3.9</v>
@@ -1055,31 +1122,31 @@
         <v>13.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.293</v>
+        <v>0.294</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P4" t="n">
         <v>21.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R4" t="n">
         <v>10.4</v>
       </c>
       <c r="S4" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T4" t="n">
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>6.1</v>
@@ -1091,19 +1158,19 @@
         <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>86.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.9</v>
+        <v>-13.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1127,7 +1194,7 @@
         <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
         <v>27</v>
@@ -1157,7 +1224,7 @@
         <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>12</v>
@@ -1306,7 +1373,7 @@
         <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1318,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP5" t="n">
         <v>21</v>
@@ -1336,13 +1403,13 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1456,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J6" t="n">
         <v>81.2</v>
@@ -1413,19 +1480,19 @@
         <v>0.423</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0.717</v>
@@ -1434,19 +1501,19 @@
         <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T6" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U6" t="n">
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X6" t="n">
         <v>4</v>
@@ -1455,19 +1522,19 @@
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
         <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1482,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="AI6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1491,13 +1558,13 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1512,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -1664,13 +1731,13 @@
         <v>3</v>
       </c>
       <c r="AI7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK7" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18</v>
       </c>
       <c r="AL7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1879,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.369</v>
+        <v>0.375</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1956,31 +2023,31 @@
         <v>79.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M9" t="n">
         <v>13.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O9" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P9" t="n">
         <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S9" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T9" t="n">
         <v>40.2</v>
@@ -1995,25 +2062,25 @@
         <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="AC9" t="n">
         <v>-5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
@@ -2025,13 +2092,13 @@
         <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
@@ -2043,10 +2110,10 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
@@ -2055,7 +2122,7 @@
         <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2073,19 +2140,19 @@
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
@@ -2258,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
         <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.646</v>
+        <v>0.641</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
@@ -2499,67 +2566,67 @@
         <v>35.7</v>
       </c>
       <c r="J12" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
         <v>16.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O12" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P12" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S12" t="n">
         <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>18.6</v>
       </c>
       <c r="V12" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W12" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC12" t="n">
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI12" t="n">
         <v>21</v>
@@ -2580,7 +2647,7 @@
         <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2589,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2601,13 +2668,13 @@
         <v>3</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
         <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>28</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2631,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
@@ -2765,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
@@ -2789,7 +2856,7 @@
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
@@ -2807,7 +2874,7 @@
         <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2947,7 +3014,7 @@
         <v>9</v>
       </c>
       <c r="AL14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM14" t="n">
         <v>19</v>
@@ -2977,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2995,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.615</v>
+        <v>0.609</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3057,13 +3124,13 @@
         <v>12.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P15" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0.758</v>
@@ -3084,7 +3151,7 @@
         <v>14.5</v>
       </c>
       <c r="W15" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X15" t="n">
         <v>5.2</v>
@@ -3099,16 +3166,16 @@
         <v>19.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
@@ -3117,7 +3184,7 @@
         <v>8</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3138,13 +3205,13 @@
         <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
@@ -3159,7 +3226,7 @@
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>6.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3326,16 +3393,16 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS16" t="n">
         <v>12</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
         <v>19</v>
@@ -3353,7 +3420,7 @@
         <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>8</v>
@@ -3362,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" t="n">
         <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.484</v>
+        <v>0.476</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J17" t="n">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6.7</v>
@@ -3424,10 +3491,10 @@
         <v>0.345</v>
       </c>
       <c r="O17" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P17" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0.777</v>
@@ -3442,34 +3509,34 @@
         <v>42.2</v>
       </c>
       <c r="U17" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3496,22 +3563,22 @@
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN17" t="n">
         <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
         <v>21</v>
@@ -3535,13 +3602,13 @@
         <v>5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3730,7 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>22</v>
@@ -3699,7 +3766,7 @@
         <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
         <v>25</v>
@@ -3711,7 +3778,7 @@
         <v>26</v>
       </c>
       <c r="AX18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -3755,46 +3822,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J19" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.427</v>
       </c>
       <c r="L19" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P19" t="n">
         <v>21.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
         <v>11.9</v>
@@ -3806,13 +3873,13 @@
         <v>40.4</v>
       </c>
       <c r="U19" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -3824,16 +3891,16 @@
         <v>19.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>24</v>
@@ -3857,13 +3924,13 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,7 +3939,7 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>11</v>
@@ -3884,25 +3951,25 @@
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV19" t="n">
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>14</v>
@@ -4209,7 +4276,7 @@
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>20</v>
@@ -4248,7 +4315,7 @@
         <v>17</v>
       </c>
       <c r="AU21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
         <v>29</v>
@@ -4257,7 +4324,7 @@
         <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4397,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
@@ -4573,10 +4640,10 @@
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -4621,7 +4688,7 @@
         <v>25</v>
       </c>
       <c r="AX23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
         <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J24" t="n">
         <v>83.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L24" t="n">
         <v>5.3</v>
@@ -4704,25 +4771,25 @@
         <v>18.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="R24" t="n">
         <v>10.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U24" t="n">
         <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="W24" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X24" t="n">
         <v>5.2</v>
@@ -4737,34 +4804,34 @@
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
         <v>24</v>
@@ -4785,13 +4852,13 @@
         <v>22</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4806,7 +4873,7 @@
         <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>17</v>
@@ -4964,7 +5031,7 @@
         <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -4973,7 +5040,7 @@
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>0.431</v>
+        <v>0.438</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,37 +5114,37 @@
         <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N26" t="n">
         <v>0.348</v>
       </c>
       <c r="O26" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.796</v>
+        <v>0.795</v>
       </c>
       <c r="R26" t="n">
         <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T26" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U26" t="n">
         <v>20.4</v>
@@ -5098,16 +5165,16 @@
         <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,16 +5186,16 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK26" t="n">
         <v>18</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>9</v>
@@ -5137,13 +5204,13 @@
         <v>8</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5170,16 +5237,16 @@
         <v>17</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -5289,22 +5356,22 @@
         <v>-6</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH27" t="n">
         <v>24</v>
       </c>
-      <c r="AG27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>23</v>
-      </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5355,16 +5422,16 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
         <v>8</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.75</v>
+        <v>0.746</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J28" t="n">
         <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.479</v>
+        <v>0.477</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.396</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
         <v>16.1</v>
@@ -5438,49 +5505,49 @@
         <v>10.2</v>
       </c>
       <c r="S28" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T28" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V28" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.5</v>
+        <v>103.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>1</v>
       </c>
       <c r="AG28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
         <v>16</v>
@@ -5507,7 +5574,7 @@
         <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>20</v>
@@ -5516,22 +5583,22 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
@@ -5546,7 +5613,7 @@
         <v>2</v>
       </c>
       <c r="BC28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
         <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,7 +5660,7 @@
         <v>34.3</v>
       </c>
       <c r="J29" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="K29" t="n">
         <v>0.44</v>
@@ -5602,16 +5669,16 @@
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O29" t="n">
         <v>16.5</v>
       </c>
       <c r="P29" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0.769</v>
@@ -5620,16 +5687,16 @@
         <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T29" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
         <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
@@ -5641,19 +5708,19 @@
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="AC29" t="n">
         <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
@@ -5665,10 +5732,10 @@
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
@@ -5677,7 +5744,7 @@
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="n">
         <v>21</v>
@@ -5689,25 +5756,25 @@
         <v>16</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ29" t="n">
         <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
         <v>15</v>
       </c>
       <c r="AV29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
@@ -5725,10 +5792,10 @@
         <v>26</v>
       </c>
       <c r="BB29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
@@ -5883,7 +5950,7 @@
         <v>15</v>
       </c>
       <c r="AT30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
         <v>11</v>
@@ -5907,7 +5974,7 @@
         <v>7</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
         <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.281</v>
+        <v>0.27</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M31" t="n">
         <v>16.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.319</v>
+        <v>0.323</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
         <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T31" t="n">
         <v>41.5</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X31" t="n">
         <v>6.4</v>
@@ -6008,16 +6075,16 @@
         <v>21.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,13 +6099,13 @@
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>6</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6050,7 +6117,7 @@
         <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
         <v>24</v>
@@ -6059,7 +6126,7 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
         <v>20</v>
@@ -6092,7 +6159,7 @@
         <v>24</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-23-2011-12</t>
+          <t>2012-04-23</t>
         </is>
       </c>
     </row>
